--- a/Documents/Planning/平台与权限/多语言翻译总表_v1.xlsx
+++ b/Documents/Planning/平台与权限/多语言翻译总表_v1.xlsx
@@ -1118,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5556,6 +5556,102 @@
       <c r="F154" t="inlineStr">
         <is>
           <t>entity_20260626_peter_trans</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Coface 下单状态</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Coface Order Status</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Coface系统内下单（2026-08-01）</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>entity_20260727_peter</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>mcs_cofaceordermsg</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Coface 下单信息</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Coface Order Info</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Coface系统内下单（2026-08-01）</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>entity_20260727_peter</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderdate</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Coface 下单时间</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Coface Order Date</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Coface系统内下单（2026-08-01）</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>entity_20260727_peter</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6661,6 +6757,186 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>未下单</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Not Ordered</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-01 DEV1 双语已设（公共方法 value==0 跳过 bug 已修复）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>调查单已提交</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Identification Order Submitted</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-01 DEV1 双语已设</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>URBA已下单待就绪</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>URBA Ordered, Pending</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-01 DEV1 双语已设</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Report已下单待就绪</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Report Ordered, Pending</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-01 DEV1 双语已设</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>已就绪</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-01 DEV1 双语已设</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>mcs_credit_record</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>mcs_cofaceorderstatus</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>下单失败</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Order Failed</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-01 DEV1 双语已设</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8891,6 +9167,28 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>mcs_credititem_value 当前无自定义 App Action 按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mcs_credit_record_place_coface_order</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Coface 下单</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Place Coface Order</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-01 最终定稿 App Action（fonticon=ShoppingCart）；曾短暂 Ribbon 化后回退，环境残留已用 ValueRule 恒否规则隐藏并从 entity_20260727_peter 剥净</t>
         </is>
       </c>
     </row>
@@ -8905,7 +9203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10008,6 +10306,336 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStatus_0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>未下单</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Not Ordered</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStatus_1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>调查单已提交</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Identification Order Submitted</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStatus_2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>URBA已下单待就绪</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>URBA Ordered, Pending</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStatus_3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Report已下单待就绪</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Report Ordered, Pending</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStatus_4</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>已就绪</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStatus_5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>下单失败</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Order Failed</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderStageLimit</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>【Coface 下单】仅在关联客户代码阶段可用</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[Place Coface Order] is only available in the Link Customer Code stage.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderNoCofaceId</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>未关联科法斯客户，请先执行【搜索 Coface 企业】绑定 Coface ID</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>No Coface company is linked. Please bind a Coface ID via [Search Coface Company] first.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderPlacing</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>正在执行 Coface 下单/状态查询，请稍候...</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Placing Coface order / checking status, please wait...</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderChecking</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>正在查询 Coface 订单状态，请稍候...</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Checking Coface order status, please wait...</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderBlocked</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Coface 订单未就绪，无法进入内外部数据集成阶段。请等待订单完成后重试。</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>The Coface order is not ready. Cannot proceed to the data integration stage. Please retry after the order is completed.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderCurrentStatusPrefix</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>当前下单状态：</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current order status: </t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderFailedPrefix</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Coface 下单失败：</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coface order failed: </t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderCheckFailed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Coface 订单状态查询失败，请稍后再试：</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failed to check Coface order status. Please try again later: </t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CreditRecord_CofaceOrderAbnormal</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coface 下单接口返回异常</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>The Coface order API returned an abnormal response</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mcs_credit_record.js（Coface系统内下单，2026-08-01；已入仓库语言文件分支 uat-20260801-peter-langfile-cofaceorder）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
